--- a/doc/bom.xlsx
+++ b/doc/bom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/29207b9eabef3a75/Repositories/androphage/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="158" documentId="13_ncr:1_{80A6E519-0331-4A1D-8CAF-BF25CB7DC384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE845339-7C99-451B-A02B-589DFBCD42AD}"/>
+  <xr:revisionPtr revIDLastSave="170" documentId="13_ncr:1_{80A6E519-0331-4A1D-8CAF-BF25CB7DC384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B73F323-892E-46E9-8BBF-5B6639DE6465}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{8DB1EDA4-4242-4AFC-9D80-17DA06623A1E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="210">
   <si>
     <t>Part</t>
   </si>
@@ -660,6 +660,15 @@
   </si>
   <si>
     <t xml:space="preserve">757-TCR2EF19LMCT </t>
+  </si>
+  <si>
+    <t>O-Ring</t>
+  </si>
+  <si>
+    <t>150 mm x 3.5 mm</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0eipM3TN</t>
   </si>
 </sst>
 </file>
@@ -711,12 +720,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -751,15 +761,11 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9EABCF6B-F62E-4CEF-876F-C6703C2CB05B}" name="Table1" displayName="Table1" ref="A1:O60" totalsRowCount="1">
-  <autoFilter ref="A1:O59" xr:uid="{9EABCF6B-F62E-4CEF-876F-C6703C2CB05B}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O59">
-    <sortCondition ref="L1:L59"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9EABCF6B-F62E-4CEF-876F-C6703C2CB05B}" name="Table1" displayName="Table1" ref="A1:O61" totalsRowCount="1">
+  <autoFilter ref="A1:O60" xr:uid="{9EABCF6B-F62E-4CEF-876F-C6703C2CB05B}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O60">
+    <sortCondition ref="M1:M60"/>
   </sortState>
   <tableColumns count="15">
     <tableColumn id="3" xr3:uid="{3F936F54-9C17-413F-9E9B-EB050C4288F3}" name="Part" totalsRowFunction="count"/>
@@ -1103,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16F71132-6C41-404D-9956-FBB395F69D1A}">
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.6640625" bestFit="1" customWidth="1"/>
@@ -1170,68 +1176,68 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
       </c>
       <c r="J2">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="4">
-        <v>0.1</v>
+        <v>2.64</v>
       </c>
       <c r="L2" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>124</v>
+        <v>37</v>
+      </c>
+      <c r="O2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
+        <v>164</v>
+      </c>
+      <c r="B3" t="s">
+        <v>165</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
       </c>
       <c r="J3">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K3" s="4">
-        <v>0.1</v>
+        <v>1.21</v>
       </c>
       <c r="L3" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.1</v>
+        <v>4.84</v>
       </c>
       <c r="M3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C4" t="s">
-        <v>197</v>
-      </c>
-      <c r="G4">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
       <c r="J4">
@@ -1239,55 +1245,60 @@
         <v>1</v>
       </c>
       <c r="K4" s="4">
-        <v>0.1</v>
+        <v>3.52</v>
       </c>
       <c r="L4" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.1</v>
+        <v>3.52</v>
       </c>
       <c r="M4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C5" t="s">
-        <v>198</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
       </c>
       <c r="J5">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="4">
-        <v>0.1</v>
+        <v>5.9</v>
       </c>
       <c r="L5" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.1</v>
+        <v>11.8</v>
       </c>
       <c r="M5" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>152</v>
-      </c>
-      <c r="C6" t="s">
-        <v>199</v>
-      </c>
-      <c r="G6">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6">
         <v>1</v>
       </c>
       <c r="J6">
@@ -1295,447 +1306,399 @@
         <v>1</v>
       </c>
       <c r="K6" s="4">
-        <v>0.1</v>
+        <v>7.99</v>
       </c>
       <c r="L6" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.1</v>
+        <v>7.99</v>
       </c>
       <c r="M6" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>131</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C7" t="s">
-        <v>201</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7">
+        <v>32</v>
       </c>
       <c r="J7">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="K7" s="4">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="L7" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.1</v>
+        <v>1.28</v>
       </c>
       <c r="M7" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>158</v>
-      </c>
-      <c r="C8" t="s">
-        <v>202</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
+        <v>77</v>
+      </c>
+      <c r="G8">
+        <v>44</v>
       </c>
       <c r="J8">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="K8" s="4">
-        <v>0.1</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="L8" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.1</v>
+        <v>6.16</v>
       </c>
       <c r="M8" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" s="4">
-        <v>0.03</v>
+        <v>0.39</v>
       </c>
       <c r="L9" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="M9" t="s">
         <v>14</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>147</v>
+        <v>21</v>
+      </c>
+      <c r="O9" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" t="s">
-        <v>173</v>
-      </c>
-      <c r="D10" t="s">
-        <v>113</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
+        <v>81</v>
+      </c>
+      <c r="I10">
+        <v>4</v>
       </c>
       <c r="J10">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K10" s="4">
-        <v>0.18</v>
+        <v>0.03</v>
       </c>
       <c r="L10" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="M10" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>153</v>
-      </c>
-      <c r="C11" t="s">
-        <v>200</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11">
+        <v>6</v>
       </c>
       <c r="J11">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K11" s="4">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="L11" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="M11" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>139</v>
-      </c>
-      <c r="C12" t="s">
-        <v>176</v>
-      </c>
-      <c r="H12">
-        <v>2</v>
+        <v>82</v>
+      </c>
+      <c r="B12" t="s">
+        <v>83</v>
+      </c>
+      <c r="I12">
+        <v>26</v>
       </c>
       <c r="J12">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="K12" s="4">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="L12" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.24</v>
+        <v>2.08</v>
       </c>
       <c r="M12" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>140</v>
-      </c>
-      <c r="C13" t="s">
-        <v>177</v>
-      </c>
-      <c r="D13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H13">
-        <v>2</v>
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
       </c>
       <c r="J13">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" s="4">
-        <v>0.12</v>
+        <v>11.99</v>
       </c>
       <c r="L13" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>142</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" t="s">
-        <v>206</v>
-      </c>
-      <c r="D14" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14">
-        <v>2</v>
-      </c>
-      <c r="J14">
+        <v>207</v>
+      </c>
+      <c r="B14" t="s">
+        <v>208</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14" s="5">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
         <v>2</v>
       </c>
       <c r="K14" s="4">
-        <v>0.14000000000000001</v>
+        <v>1</v>
       </c>
       <c r="L14" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.28000000000000003</v>
+        <v>2</v>
       </c>
       <c r="M14" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="O14" t="s">
-        <v>50</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" t="s">
-        <v>203</v>
-      </c>
-      <c r="D15" t="s">
-        <v>110</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
+        <v>75</v>
+      </c>
+      <c r="B15" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
       </c>
       <c r="J15">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" s="4">
-        <v>0.28999999999999998</v>
+        <v>7.42</v>
       </c>
       <c r="L15" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.28999999999999998</v>
+        <v>14.84</v>
       </c>
       <c r="M15" t="s">
-        <v>8</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>133</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>154</v>
-      </c>
-      <c r="C16" t="s">
-        <v>196</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="H16">
-        <v>2</v>
+        <v>160</v>
+      </c>
+      <c r="B16" t="s">
+        <v>78</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
       </c>
       <c r="J16">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K16" s="4">
-        <v>0.1</v>
+        <v>21.24</v>
       </c>
       <c r="L16" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.30000000000000004</v>
+        <v>21.24</v>
       </c>
       <c r="M16" t="s">
-        <v>8</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" t="s">
-        <v>181</v>
-      </c>
-      <c r="D17" t="s">
-        <v>96</v>
-      </c>
-      <c r="E17">
-        <v>2</v>
-      </c>
-      <c r="G17">
+        <v>159</v>
+      </c>
+      <c r="B17" t="s">
+        <v>78</v>
+      </c>
+      <c r="I17">
         <v>1</v>
       </c>
       <c r="J17">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K17" s="4">
-        <v>0.11</v>
+        <v>21.24</v>
       </c>
       <c r="L17" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.33</v>
+        <v>21.24</v>
       </c>
       <c r="M17" t="s">
-        <v>8</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" t="s">
-        <v>191</v>
-      </c>
-      <c r="D18" t="s">
-        <v>109</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>88</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
       </c>
       <c r="J18">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" s="4">
-        <v>0.33</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="L18" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.33</v>
+        <v>9.1199999999999992</v>
       </c>
       <c r="M18" t="s">
-        <v>8</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>192</v>
+        <v>31</v>
+      </c>
+      <c r="O18" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
-      </c>
-      <c r="I19">
-        <v>6</v>
+        <v>45</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
       </c>
       <c r="J19">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K19" s="4">
-        <v>0.06</v>
+        <v>0.63</v>
       </c>
       <c r="L19" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.36</v>
+        <v>1.26</v>
       </c>
       <c r="M19" t="s">
-        <v>14</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>162</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" t="s">
-        <v>205</v>
-      </c>
-      <c r="D20" t="s">
-        <v>112</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
       </c>
       <c r="J20">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" s="4">
-        <v>0.37</v>
+        <v>1.97</v>
       </c>
       <c r="L20" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.37</v>
+        <v>3.94</v>
       </c>
       <c r="M20" t="s">
-        <v>8</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" t="s">
-        <v>204</v>
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
+        <v>48</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1745,28 +1708,22 @@
         <v>1</v>
       </c>
       <c r="K21" s="4">
-        <v>0.52</v>
+        <v>5.13</v>
       </c>
       <c r="L21" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.52</v>
+        <v>5.13</v>
       </c>
       <c r="M21" t="s">
-        <v>8</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>163</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>103</v>
-      </c>
-      <c r="C22" t="s">
-        <v>189</v>
-      </c>
-      <c r="D22" t="s">
-        <v>106</v>
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
+        <v>47</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1776,87 +1733,75 @@
         <v>1</v>
       </c>
       <c r="K22" s="4">
-        <v>0.54</v>
+        <v>5.45</v>
       </c>
       <c r="L22" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.54</v>
+        <v>5.45</v>
       </c>
       <c r="M22" t="s">
-        <v>8</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="O22" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>137</v>
-      </c>
-      <c r="C23" t="s">
-        <v>175</v>
-      </c>
-      <c r="D23" t="s">
-        <v>53</v>
-      </c>
-      <c r="F23">
-        <v>2</v>
-      </c>
-      <c r="H23">
-        <v>4</v>
+        <v>30</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
       </c>
       <c r="J23">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K23" s="4">
-        <v>0.1</v>
+        <v>0.66</v>
       </c>
       <c r="L23" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.60000000000000009</v>
+        <v>0.66</v>
       </c>
       <c r="M23" t="s">
-        <v>8</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>143</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>145</v>
+      </c>
+      <c r="B24" t="s">
+        <v>93</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J24">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K24" s="4">
-        <v>0.66</v>
+        <v>0.45</v>
       </c>
       <c r="L24" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.66</v>
+        <v>3.6</v>
       </c>
       <c r="M24" t="s">
-        <v>17</v>
+        <v>135</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="C25" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="D25" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -1866,33 +1811,30 @@
         <v>1</v>
       </c>
       <c r="K25" s="4">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="L25" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="M25" t="s">
         <v>8</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="O25" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D26" t="s">
-        <v>102</v>
-      </c>
-      <c r="F26">
+        <v>113</v>
+      </c>
+      <c r="G26">
         <v>1</v>
       </c>
       <c r="J26">
@@ -1900,121 +1842,121 @@
         <v>1</v>
       </c>
       <c r="K26" s="4">
-        <v>0.76</v>
+        <v>0.18</v>
       </c>
       <c r="L26" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.76</v>
+        <v>0.18</v>
       </c>
       <c r="M26" t="s">
         <v>8</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>101</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C27" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D27" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J27">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K27" s="4">
-        <v>0.38</v>
+        <v>0.1</v>
       </c>
       <c r="L27" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="M27" t="s">
         <v>8</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="C28" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="D28" t="s">
-        <v>120</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
+        <v>53</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="H28">
+        <v>4</v>
       </c>
       <c r="J28">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K28" s="4">
-        <v>0.76</v>
+        <v>0.1</v>
       </c>
       <c r="L28" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.76</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="M28" t="s">
         <v>8</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C29" t="s">
-        <v>174</v>
-      </c>
-      <c r="D29" t="s">
-        <v>51</v>
+        <v>176</v>
       </c>
       <c r="H29">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J29">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K29" s="4">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="L29" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.8</v>
+        <v>0.24</v>
       </c>
       <c r="M29" t="s">
         <v>8</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="C30" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D30" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H30">
         <v>2</v>
@@ -2024,381 +1966,420 @@
         <v>2</v>
       </c>
       <c r="K30" s="4">
-        <v>0.4</v>
+        <v>0.12</v>
       </c>
       <c r="L30" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.8</v>
+        <v>0.24</v>
       </c>
       <c r="M30" t="s">
         <v>8</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>98</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>141</v>
       </c>
       <c r="C31" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D31" t="s">
-        <v>95</v>
-      </c>
-      <c r="E31">
-        <v>2</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
+        <v>54</v>
+      </c>
+      <c r="H31">
+        <v>2</v>
       </c>
       <c r="J31">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K31" s="4">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="L31" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.96</v>
+        <v>0.76</v>
       </c>
       <c r="M31" t="s">
         <v>8</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>150</v>
+        <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>193</v>
+        <v>179</v>
+      </c>
+      <c r="D32" t="s">
+        <v>115</v>
       </c>
       <c r="G32">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="J32">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="K32" s="4">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="L32" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>1.2000000000000002</v>
+        <v>4.84</v>
       </c>
       <c r="M32" t="s">
         <v>8</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>129</v>
+        <v>114</v>
+      </c>
+      <c r="O32" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" t="s">
-        <v>45</v>
-      </c>
-      <c r="H33">
-        <v>2</v>
+        <v>61</v>
+      </c>
+      <c r="C33" t="s">
+        <v>180</v>
+      </c>
+      <c r="D33" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33">
+        <v>6</v>
       </c>
       <c r="J33">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K33" s="4">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="L33" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>1.26</v>
+        <v>5.34</v>
       </c>
       <c r="M33" t="s">
-        <v>17</v>
+        <v>8</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" t="s">
-        <v>85</v>
-      </c>
-      <c r="I34">
-        <v>32</v>
+        <v>60</v>
+      </c>
+      <c r="C34" t="s">
+        <v>181</v>
+      </c>
+      <c r="D34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34">
+        <v>2</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
       </c>
       <c r="J34">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K34" s="4">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="L34" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>1.28</v>
+        <v>0.33</v>
       </c>
       <c r="M34" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>148</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>82</v>
-      </c>
-      <c r="B35" t="s">
-        <v>83</v>
+        <v>7</v>
+      </c>
+      <c r="C35" t="s">
+        <v>182</v>
+      </c>
+      <c r="D35" t="s">
+        <v>122</v>
       </c>
       <c r="I35">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="J35">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="K35" s="4">
-        <v>0.08</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="L35" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>2.08</v>
+        <v>7.9099999999999993</v>
       </c>
       <c r="M35" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>161</v>
+        <v>121</v>
+      </c>
+      <c r="O35" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D36" t="s">
-        <v>117</v>
-      </c>
-      <c r="G36">
-        <v>2</v>
+        <v>99</v>
+      </c>
+      <c r="E36">
+        <v>2</v>
+      </c>
+      <c r="F36">
+        <v>8</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
       </c>
       <c r="J36">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K36" s="4">
-        <v>1.69</v>
+        <v>0.43</v>
       </c>
       <c r="L36" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>3.38</v>
+        <v>4.7299999999999995</v>
       </c>
       <c r="M36" t="s">
         <v>8</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>10</v>
-      </c>
-      <c r="B37" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37">
-        <v>1</v>
+        <v>94</v>
+      </c>
+      <c r="C37" t="s">
+        <v>184</v>
+      </c>
+      <c r="D37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H37">
+        <v>2</v>
       </c>
       <c r="J37">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K37" s="4">
-        <v>3.52</v>
+        <v>0.4</v>
       </c>
       <c r="L37" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>3.52</v>
+        <v>0.8</v>
       </c>
       <c r="M37" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>145</v>
-      </c>
-      <c r="B38" t="s">
-        <v>93</v>
-      </c>
-      <c r="I38">
-        <v>8</v>
+        <v>59</v>
+      </c>
+      <c r="C38" t="s">
+        <v>185</v>
+      </c>
+      <c r="D38" t="s">
+        <v>95</v>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
       </c>
       <c r="J38">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K38" s="4">
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="L38" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>3.6</v>
+        <v>0.96</v>
       </c>
       <c r="M38" t="s">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>44</v>
-      </c>
-      <c r="B39" t="s">
-        <v>46</v>
-      </c>
-      <c r="E39">
-        <v>2</v>
+        <v>166</v>
+      </c>
+      <c r="C39" t="s">
+        <v>186</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
       </c>
       <c r="J39">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K39" s="4">
-        <v>1.97</v>
+        <v>9.11</v>
       </c>
       <c r="L39" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>3.94</v>
+        <v>9.11</v>
       </c>
       <c r="M39" t="s">
-        <v>17</v>
+        <v>8</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="C40" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D40" t="s">
-        <v>99</v>
-      </c>
-      <c r="E40">
-        <v>2</v>
-      </c>
-      <c r="F40">
-        <v>8</v>
-      </c>
-      <c r="I40">
-        <v>1</v>
+        <v>117</v>
+      </c>
+      <c r="G40">
+        <v>2</v>
       </c>
       <c r="J40">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K40" s="4">
-        <v>0.43</v>
+        <v>1.69</v>
       </c>
       <c r="L40" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>4.7299999999999995</v>
+        <v>3.38</v>
       </c>
       <c r="M40" t="s">
         <v>8</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>164</v>
-      </c>
-      <c r="B41" t="s">
-        <v>165</v>
-      </c>
-      <c r="I41">
-        <v>4</v>
+        <v>70</v>
+      </c>
+      <c r="C41" t="s">
+        <v>188</v>
+      </c>
+      <c r="D41" t="s">
+        <v>120</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
       </c>
       <c r="J41">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K41" s="4">
-        <v>1.21</v>
+        <v>0.76</v>
       </c>
       <c r="L41" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>4.84</v>
+        <v>0.76</v>
       </c>
       <c r="M41" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="C42" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="D42" t="s">
-        <v>115</v>
-      </c>
-      <c r="G42">
-        <v>44</v>
+        <v>106</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
       </c>
       <c r="J42">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="K42" s="4">
-        <v>0.11</v>
+        <v>0.54</v>
       </c>
       <c r="L42" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>4.84</v>
+        <v>0.54</v>
       </c>
       <c r="M42" t="s">
         <v>8</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="O42" t="s">
-        <v>116</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43" t="s">
-        <v>48</v>
-      </c>
-      <c r="G43">
+        <v>104</v>
+      </c>
+      <c r="C43" t="s">
+        <v>190</v>
+      </c>
+      <c r="D43" t="s">
+        <v>107</v>
+      </c>
+      <c r="F43">
         <v>1</v>
       </c>
       <c r="J43">
@@ -2406,169 +2387,176 @@
         <v>1</v>
       </c>
       <c r="K43" s="4">
-        <v>5.13</v>
+        <v>0.74</v>
       </c>
       <c r="L43" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>5.13</v>
+        <v>0.74</v>
       </c>
       <c r="M43" t="s">
-        <v>17</v>
+        <v>8</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="O43" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C44" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="D44" t="s">
-        <v>90</v>
-      </c>
-      <c r="E44">
-        <v>6</v>
+        <v>109</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
       </c>
       <c r="J44">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K44" s="4">
-        <v>0.89</v>
+        <v>0.33</v>
       </c>
       <c r="L44" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>5.34</v>
+        <v>0.33</v>
       </c>
       <c r="M44" t="s">
         <v>8</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
-        <v>47</v>
-      </c>
-      <c r="F45">
-        <v>1</v>
+        <v>150</v>
+      </c>
+      <c r="C45" t="s">
+        <v>193</v>
+      </c>
+      <c r="G45">
+        <v>12</v>
       </c>
       <c r="J45">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K45" s="4">
-        <v>5.45</v>
+        <v>0.1</v>
       </c>
       <c r="L45" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>5.45</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="M45" t="s">
-        <v>17</v>
+        <v>8</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>77</v>
-      </c>
-      <c r="G46">
-        <v>44</v>
+        <v>155</v>
+      </c>
+      <c r="C46" t="s">
+        <v>194</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
       </c>
       <c r="J46">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="K46" s="4">
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="L46" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>6.16</v>
+        <v>0.1</v>
       </c>
       <c r="M46" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>76</v>
-      </c>
-      <c r="B47" t="s">
-        <v>74</v>
-      </c>
-      <c r="I47">
-        <v>2</v>
+        <v>156</v>
+      </c>
+      <c r="C47" t="s">
+        <v>195</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
       </c>
       <c r="J47">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K47" s="4">
-        <v>3.45</v>
+        <v>0.1</v>
       </c>
       <c r="L47" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>6.9</v>
+        <v>0.1</v>
       </c>
       <c r="M47" t="s">
-        <v>33</v>
+        <v>8</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>7</v>
+        <v>154</v>
       </c>
       <c r="C48" t="s">
-        <v>182</v>
-      </c>
-      <c r="D48" t="s">
-        <v>122</v>
-      </c>
-      <c r="I48">
-        <v>7</v>
+        <v>196</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>2</v>
       </c>
       <c r="J48">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K48" s="4">
-        <v>1.1299999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="L48" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>7.9099999999999993</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="M48" t="s">
         <v>8</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="O48" t="s">
-        <v>56</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>13</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49">
+        <v>149</v>
+      </c>
+      <c r="C49" t="s">
+        <v>197</v>
+      </c>
+      <c r="G49">
         <v>1</v>
       </c>
       <c r="J49">
@@ -2576,27 +2564,27 @@
         <v>1</v>
       </c>
       <c r="K49" s="4">
-        <v>7.99</v>
+        <v>0.1</v>
       </c>
       <c r="L49" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>7.99</v>
+        <v>0.1</v>
       </c>
       <c r="M49" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C50" t="s">
-        <v>186</v>
-      </c>
-      <c r="F50">
+        <v>198</v>
+      </c>
+      <c r="G50">
         <v>1</v>
       </c>
       <c r="J50">
@@ -2604,55 +2592,55 @@
         <v>1</v>
       </c>
       <c r="K50" s="4">
-        <v>9.11</v>
+        <v>0.1</v>
       </c>
       <c r="L50" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>9.11</v>
+        <v>0.1</v>
       </c>
       <c r="M50" t="s">
         <v>8</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>19</v>
+        <v>130</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>32</v>
-      </c>
-      <c r="B51" t="s">
-        <v>88</v>
-      </c>
-      <c r="I51">
-        <v>2</v>
+        <v>152</v>
+      </c>
+      <c r="C51" t="s">
+        <v>199</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
       </c>
       <c r="J51">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K51" s="4">
-        <v>4.5599999999999996</v>
+        <v>0.1</v>
       </c>
       <c r="L51" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>9.1199999999999992</v>
+        <v>0.1</v>
       </c>
       <c r="M51" t="s">
-        <v>31</v>
-      </c>
-      <c r="O51" t="s">
-        <v>87</v>
+        <v>8</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>27</v>
-      </c>
-      <c r="B52" t="s">
-        <v>28</v>
-      </c>
-      <c r="H52">
+        <v>153</v>
+      </c>
+      <c r="C52" t="s">
+        <v>200</v>
+      </c>
+      <c r="G52">
         <v>2</v>
       </c>
       <c r="J52">
@@ -2660,27 +2648,27 @@
         <v>2</v>
       </c>
       <c r="K52" s="4">
-        <v>5.9</v>
+        <v>0.1</v>
       </c>
       <c r="L52" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>11.8</v>
+        <v>0.2</v>
       </c>
       <c r="M52" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>71</v>
+        <v>132</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" t="s">
-        <v>40</v>
-      </c>
-      <c r="I53">
+        <v>157</v>
+      </c>
+      <c r="C53" t="s">
+        <v>201</v>
+      </c>
+      <c r="F53">
         <v>1</v>
       </c>
       <c r="J53">
@@ -2688,80 +2676,86 @@
         <v>1</v>
       </c>
       <c r="K53" s="4">
-        <v>11.99</v>
+        <v>0.1</v>
       </c>
       <c r="L53" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>11.99</v>
+        <v>0.1</v>
       </c>
       <c r="M53" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>34</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>75</v>
-      </c>
-      <c r="B54" t="s">
-        <v>78</v>
-      </c>
-      <c r="I54">
-        <v>2</v>
+        <v>158</v>
+      </c>
+      <c r="C54" t="s">
+        <v>202</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
       </c>
       <c r="J54">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K54" s="4">
-        <v>7.42</v>
+        <v>0.1</v>
       </c>
       <c r="L54" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>14.84</v>
+        <v>0.1</v>
       </c>
       <c r="M54" t="s">
-        <v>31</v>
+        <v>8</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>79</v>
-      </c>
-      <c r="I55">
-        <v>44</v>
+        <v>65</v>
+      </c>
+      <c r="C55" t="s">
+        <v>203</v>
+      </c>
+      <c r="D55" t="s">
+        <v>110</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
       </c>
       <c r="J55">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="K55" s="4">
-        <v>0.39</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="L55" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>17.16</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M55" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O55" t="s">
-        <v>86</v>
+        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>22</v>
-      </c>
-      <c r="B56" t="s">
-        <v>23</v>
-      </c>
-      <c r="I56">
+        <v>69</v>
+      </c>
+      <c r="C56" t="s">
+        <v>204</v>
+      </c>
+      <c r="G56">
         <v>1</v>
       </c>
       <c r="J56">
@@ -2769,52 +2763,64 @@
         <v>1</v>
       </c>
       <c r="K56" s="4">
-        <v>20</v>
+        <v>0.52</v>
       </c>
       <c r="L56" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>20</v>
+        <v>0.52</v>
       </c>
       <c r="M56" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>25</v>
+        <v>163</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>160</v>
-      </c>
-      <c r="B57" t="s">
-        <v>78</v>
-      </c>
-      <c r="I57">
-        <v>1</v>
+        <v>49</v>
+      </c>
+      <c r="C57" t="s">
+        <v>206</v>
+      </c>
+      <c r="D57" t="s">
+        <v>57</v>
+      </c>
+      <c r="H57">
+        <v>2</v>
       </c>
       <c r="J57">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K57" s="4">
-        <v>21.24</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="L57" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>21.24</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="M57" t="s">
-        <v>31</v>
+        <v>8</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O57" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>159</v>
-      </c>
-      <c r="B58" t="s">
-        <v>78</v>
-      </c>
-      <c r="I58">
+        <v>49</v>
+      </c>
+      <c r="C58" t="s">
+        <v>205</v>
+      </c>
+      <c r="D58" t="s">
+        <v>112</v>
+      </c>
+      <c r="F58">
         <v>1</v>
       </c>
       <c r="J58">
@@ -2822,138 +2828,166 @@
         <v>1</v>
       </c>
       <c r="K58" s="4">
-        <v>21.24</v>
+        <v>0.37</v>
       </c>
       <c r="L58" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>21.24</v>
+        <v>0.37</v>
       </c>
       <c r="M58" t="s">
-        <v>31</v>
+        <v>8</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>35</v>
+        <v>76</v>
+      </c>
+      <c r="B59" t="s">
+        <v>74</v>
       </c>
       <c r="I59">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="J59">
         <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="K59" s="4">
-        <v>2.64</v>
+        <v>3.45</v>
       </c>
       <c r="L59" s="1">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>116.16000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="M59" t="s">
-        <v>36</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="O59" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A60">
+      <c r="A60" t="s">
+        <v>22</v>
+      </c>
+      <c r="B60" t="s">
+        <v>23</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+      <c r="J60">
+        <f>SUM(Table1[[#This Row],[Connector PCB]:[Other]])</f>
+        <v>1</v>
+      </c>
+      <c r="K60" s="4">
+        <v>20</v>
+      </c>
+      <c r="L60" s="1">
+        <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>20</v>
+      </c>
+      <c r="M60" t="s">
+        <v>24</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A61">
         <f>SUBTOTAL(103,Table1[Part])</f>
-        <v>58</v>
-      </c>
-      <c r="C60">
+        <v>59</v>
+      </c>
+      <c r="C61">
         <f>SUBTOTAL(103,Table1[Mouser Part '#])</f>
         <v>34</v>
       </c>
-      <c r="D60">
+      <c r="D61">
         <f>SUBTOTAL(103,Table1[LCSC Part '#])</f>
         <v>21</v>
       </c>
-      <c r="E60">
+      <c r="E61">
         <f>SUBTOTAL(109,Table1[Connector PCB])</f>
         <v>15</v>
       </c>
-      <c r="F60">
+      <c r="F61">
         <f>SUBTOTAL(109,Table1[Control PCB])</f>
         <v>23</v>
       </c>
-      <c r="G60">
+      <c r="G61">
         <f>SUBTOTAL(109,Table1[Matrix PCB])</f>
         <v>113</v>
       </c>
-      <c r="H60">
+      <c r="H61">
         <f>SUBTOTAL(109,Table1[Sensor PCB])</f>
         <v>28</v>
       </c>
-      <c r="I60">
+      <c r="I61">
         <f>SUBTOTAL(109,Table1[Other])</f>
-        <v>188</v>
-      </c>
-      <c r="J60">
+        <v>101</v>
+      </c>
+      <c r="J61">
         <f>SUBTOTAL(109,Table1[Quantity])</f>
-        <v>367</v>
-      </c>
-      <c r="K60" s="4"/>
-      <c r="L60" s="1">
+        <v>280</v>
+      </c>
+      <c r="K61" s="4"/>
+      <c r="L61" s="1">
         <f>SUBTOTAL(109,Table1[Total Cost])</f>
-        <v>344.05</v>
+        <v>200.73999999999998</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="N52" r:id="rId1" xr:uid="{3EF80975-0ADC-4121-AC6E-F0D6F27192AF}"/>
-    <hyperlink ref="N37" r:id="rId2" xr:uid="{9D497DA8-6AE2-4348-9482-BF079C45DDC8}"/>
-    <hyperlink ref="N41" r:id="rId3" xr:uid="{5F713AD3-EE79-419E-86E4-410E314D82F6}"/>
-    <hyperlink ref="N53" r:id="rId4" xr:uid="{B7FD5679-CB48-466D-AC82-40D5B164DF30}"/>
-    <hyperlink ref="N59" r:id="rId5" xr:uid="{BC1A73A8-5824-49FD-9174-AC378356EF75}"/>
-    <hyperlink ref="N55" r:id="rId6" xr:uid="{CE4DA7E2-CFEB-44CB-9C47-C6720CD408C4}"/>
-    <hyperlink ref="N49" r:id="rId7" xr:uid="{273FF093-11C5-4FEC-A9B0-EACAB5AB41E3}"/>
-    <hyperlink ref="N56" r:id="rId8" xr:uid="{39E26F94-7A88-4F83-A169-50F069C2667C}"/>
-    <hyperlink ref="N46" r:id="rId9" xr:uid="{D3FA6702-581A-44C3-A593-C7AFEF91EF0E}"/>
-    <hyperlink ref="N50" r:id="rId10" xr:uid="{7939374C-C62A-41FE-BFB5-01DB0961903D}"/>
-    <hyperlink ref="N44" r:id="rId11" xr:uid="{6C93B823-D8D6-4956-8486-8EB54F0576CD}"/>
-    <hyperlink ref="N17" r:id="rId12" xr:uid="{9F4FC012-F15E-4DF1-8D14-068E8537BF00}"/>
-    <hyperlink ref="N26" r:id="rId13" xr:uid="{5203D6E2-89CC-4BB3-B4F6-88BBDF80DA7C}"/>
-    <hyperlink ref="N29" r:id="rId14" xr:uid="{72A8F909-39D5-420A-8B66-7845EAEB395B}"/>
-    <hyperlink ref="N23" r:id="rId15" xr:uid="{7581AF20-7FE2-439A-A5A8-D474AA4AF9C7}"/>
-    <hyperlink ref="N13" r:id="rId16" xr:uid="{3ABE1717-A8C3-4737-8D89-FE8125CE41F9}"/>
-    <hyperlink ref="N27" r:id="rId17" xr:uid="{5C20296D-5290-4B05-AFF2-36FC1DE7159E}"/>
-    <hyperlink ref="N42" r:id="rId18" xr:uid="{2777019D-1F37-4583-B7E4-1DADC226B29D}"/>
-    <hyperlink ref="N48" r:id="rId19" xr:uid="{45D68375-618B-4640-ABD1-5F23369D1285}"/>
-    <hyperlink ref="N40" r:id="rId20" xr:uid="{92F3EDD7-A595-4AF4-B616-3F15D7013C5D}"/>
-    <hyperlink ref="N30" r:id="rId21" xr:uid="{C514DFF4-97E4-4F72-9CA3-1787D58C77CC}"/>
-    <hyperlink ref="N31" r:id="rId22" xr:uid="{465D9784-E07F-4177-93B6-A088AC1E9E87}"/>
-    <hyperlink ref="N36" r:id="rId23" xr:uid="{BD2E1E91-FBE4-45E9-B988-0FCB81C1D819}"/>
-    <hyperlink ref="N28" r:id="rId24" xr:uid="{C57EA39E-ABB1-4B5A-9057-231739EE3391}"/>
-    <hyperlink ref="N22" r:id="rId25" xr:uid="{9A76A53D-E3E4-4EC9-8EC8-2B7814A27973}"/>
-    <hyperlink ref="N25" r:id="rId26" xr:uid="{FA831E8D-9CFC-422F-BD3B-75AD38567BCA}"/>
-    <hyperlink ref="N2" r:id="rId27" xr:uid="{132B4780-8338-418F-B4FC-48747A897DA4}"/>
-    <hyperlink ref="N3" r:id="rId28" xr:uid="{FCDF02F6-1A1A-4F39-9E9A-91CF01CDDEE6}"/>
-    <hyperlink ref="N16" r:id="rId29" xr:uid="{51E92C2F-35C0-440F-ACC4-1C9CEE3093B2}"/>
-    <hyperlink ref="N7" r:id="rId30" xr:uid="{8D480B69-0CA8-4DDD-A5F6-2BEABAEFCE35}"/>
-    <hyperlink ref="N8" r:id="rId31" xr:uid="{DD89386A-EF93-42F0-BF9B-1097F7829BAC}"/>
-    <hyperlink ref="N32" r:id="rId32" xr:uid="{3AB1BD82-5A6B-4242-AB61-0D52BFF18885}"/>
-    <hyperlink ref="N4" r:id="rId33" xr:uid="{2664E122-D09D-4745-93CF-7C9300490A30}"/>
-    <hyperlink ref="N5" r:id="rId34" xr:uid="{96BB636E-39BF-45BA-9506-2AA90DA3F297}"/>
-    <hyperlink ref="N6" r:id="rId35" xr:uid="{60C72524-0E48-4AC7-9736-DED433AAF742}"/>
-    <hyperlink ref="N11" r:id="rId36" xr:uid="{74A5EE19-0AA5-4EF5-9A6D-C14BFA939F90}"/>
-    <hyperlink ref="N15" r:id="rId37" xr:uid="{D8C9F9EB-E711-42F0-98B1-FE8D9E63EB44}"/>
-    <hyperlink ref="N20" r:id="rId38" xr:uid="{09BFC6B5-89A0-41F4-B20E-96E3BEE79567}"/>
-    <hyperlink ref="N14" r:id="rId39" xr:uid="{DC5F4D60-24FB-4AD2-BB27-3BD0A8A98EAA}"/>
-    <hyperlink ref="N38" r:id="rId40" xr:uid="{54A69CC5-F91C-4A2A-A596-4FCDC84018C9}"/>
-    <hyperlink ref="N9" r:id="rId41" xr:uid="{E45ED9D9-58A2-49C4-9915-EFB07FBD22C0}"/>
-    <hyperlink ref="N34" r:id="rId42" xr:uid="{05E0FB06-EBE8-401F-9742-47D27CFF5DA2}"/>
-    <hyperlink ref="N35" r:id="rId43" xr:uid="{4E0019DB-B619-4375-A7CB-5C25A2DA8284}"/>
-    <hyperlink ref="N19" r:id="rId44" xr:uid="{B158F633-7D28-4277-A4D0-F9E64C5B4899}"/>
-    <hyperlink ref="N21" r:id="rId45" xr:uid="{AC47EAA7-FFFA-4DBA-A8AF-B047FD9CE6FA}"/>
-    <hyperlink ref="N10" r:id="rId46" xr:uid="{068CAB34-B222-4338-B349-37E057B5CC98}"/>
-    <hyperlink ref="N12" r:id="rId47" xr:uid="{8C5E588B-27FD-4B7F-BE44-A579F0F4E123}"/>
-    <hyperlink ref="N18" r:id="rId48" xr:uid="{02C2221B-7A90-45B4-B72D-7C38424ED119}"/>
+    <hyperlink ref="N5" r:id="rId1" xr:uid="{3EF80975-0ADC-4121-AC6E-F0D6F27192AF}"/>
+    <hyperlink ref="N4" r:id="rId2" xr:uid="{9D497DA8-6AE2-4348-9482-BF079C45DDC8}"/>
+    <hyperlink ref="N3" r:id="rId3" xr:uid="{5F713AD3-EE79-419E-86E4-410E314D82F6}"/>
+    <hyperlink ref="N13" r:id="rId4" xr:uid="{B7FD5679-CB48-466D-AC82-40D5B164DF30}"/>
+    <hyperlink ref="N2" r:id="rId5" xr:uid="{BC1A73A8-5824-49FD-9174-AC378356EF75}"/>
+    <hyperlink ref="N9" r:id="rId6" xr:uid="{CE4DA7E2-CFEB-44CB-9C47-C6720CD408C4}"/>
+    <hyperlink ref="N6" r:id="rId7" xr:uid="{273FF093-11C5-4FEC-A9B0-EACAB5AB41E3}"/>
+    <hyperlink ref="N60" r:id="rId8" xr:uid="{39E26F94-7A88-4F83-A169-50F069C2667C}"/>
+    <hyperlink ref="N8" r:id="rId9" xr:uid="{D3FA6702-581A-44C3-A593-C7AFEF91EF0E}"/>
+    <hyperlink ref="N39" r:id="rId10" xr:uid="{7939374C-C62A-41FE-BFB5-01DB0961903D}"/>
+    <hyperlink ref="N33" r:id="rId11" xr:uid="{6C93B823-D8D6-4956-8486-8EB54F0576CD}"/>
+    <hyperlink ref="N34" r:id="rId12" xr:uid="{9F4FC012-F15E-4DF1-8D14-068E8537BF00}"/>
+    <hyperlink ref="N25" r:id="rId13" xr:uid="{5203D6E2-89CC-4BB3-B4F6-88BBDF80DA7C}"/>
+    <hyperlink ref="N27" r:id="rId14" xr:uid="{72A8F909-39D5-420A-8B66-7845EAEB395B}"/>
+    <hyperlink ref="N28" r:id="rId15" xr:uid="{7581AF20-7FE2-439A-A5A8-D474AA4AF9C7}"/>
+    <hyperlink ref="N30" r:id="rId16" xr:uid="{3ABE1717-A8C3-4737-8D89-FE8125CE41F9}"/>
+    <hyperlink ref="N31" r:id="rId17" xr:uid="{5C20296D-5290-4B05-AFF2-36FC1DE7159E}"/>
+    <hyperlink ref="N32" r:id="rId18" xr:uid="{2777019D-1F37-4583-B7E4-1DADC226B29D}"/>
+    <hyperlink ref="N35" r:id="rId19" xr:uid="{45D68375-618B-4640-ABD1-5F23369D1285}"/>
+    <hyperlink ref="N36" r:id="rId20" xr:uid="{92F3EDD7-A595-4AF4-B616-3F15D7013C5D}"/>
+    <hyperlink ref="N37" r:id="rId21" xr:uid="{C514DFF4-97E4-4F72-9CA3-1787D58C77CC}"/>
+    <hyperlink ref="N38" r:id="rId22" xr:uid="{465D9784-E07F-4177-93B6-A088AC1E9E87}"/>
+    <hyperlink ref="N40" r:id="rId23" xr:uid="{BD2E1E91-FBE4-45E9-B988-0FCB81C1D819}"/>
+    <hyperlink ref="N41" r:id="rId24" xr:uid="{C57EA39E-ABB1-4B5A-9057-231739EE3391}"/>
+    <hyperlink ref="N42" r:id="rId25" xr:uid="{9A76A53D-E3E4-4EC9-8EC8-2B7814A27973}"/>
+    <hyperlink ref="N43" r:id="rId26" xr:uid="{FA831E8D-9CFC-422F-BD3B-75AD38567BCA}"/>
+    <hyperlink ref="N46" r:id="rId27" xr:uid="{132B4780-8338-418F-B4FC-48747A897DA4}"/>
+    <hyperlink ref="N47" r:id="rId28" xr:uid="{FCDF02F6-1A1A-4F39-9E9A-91CF01CDDEE6}"/>
+    <hyperlink ref="N48" r:id="rId29" xr:uid="{51E92C2F-35C0-440F-ACC4-1C9CEE3093B2}"/>
+    <hyperlink ref="N53" r:id="rId30" xr:uid="{8D480B69-0CA8-4DDD-A5F6-2BEABAEFCE35}"/>
+    <hyperlink ref="N54" r:id="rId31" xr:uid="{DD89386A-EF93-42F0-BF9B-1097F7829BAC}"/>
+    <hyperlink ref="N45" r:id="rId32" xr:uid="{3AB1BD82-5A6B-4242-AB61-0D52BFF18885}"/>
+    <hyperlink ref="N49" r:id="rId33" xr:uid="{2664E122-D09D-4745-93CF-7C9300490A30}"/>
+    <hyperlink ref="N50" r:id="rId34" xr:uid="{96BB636E-39BF-45BA-9506-2AA90DA3F297}"/>
+    <hyperlink ref="N51" r:id="rId35" xr:uid="{60C72524-0E48-4AC7-9736-DED433AAF742}"/>
+    <hyperlink ref="N52" r:id="rId36" xr:uid="{74A5EE19-0AA5-4EF5-9A6D-C14BFA939F90}"/>
+    <hyperlink ref="N55" r:id="rId37" xr:uid="{D8C9F9EB-E711-42F0-98B1-FE8D9E63EB44}"/>
+    <hyperlink ref="N58" r:id="rId38" xr:uid="{09BFC6B5-89A0-41F4-B20E-96E3BEE79567}"/>
+    <hyperlink ref="N57" r:id="rId39" xr:uid="{DC5F4D60-24FB-4AD2-BB27-3BD0A8A98EAA}"/>
+    <hyperlink ref="N24" r:id="rId40" xr:uid="{54A69CC5-F91C-4A2A-A596-4FCDC84018C9}"/>
+    <hyperlink ref="N10" r:id="rId41" xr:uid="{E45ED9D9-58A2-49C4-9915-EFB07FBD22C0}"/>
+    <hyperlink ref="N7" r:id="rId42" xr:uid="{05E0FB06-EBE8-401F-9742-47D27CFF5DA2}"/>
+    <hyperlink ref="N12" r:id="rId43" xr:uid="{4E0019DB-B619-4375-A7CB-5C25A2DA8284}"/>
+    <hyperlink ref="N11" r:id="rId44" xr:uid="{B158F633-7D28-4277-A4D0-F9E64C5B4899}"/>
+    <hyperlink ref="N56" r:id="rId45" xr:uid="{AC47EAA7-FFFA-4DBA-A8AF-B047FD9CE6FA}"/>
+    <hyperlink ref="N26" r:id="rId46" xr:uid="{068CAB34-B222-4338-B349-37E057B5CC98}"/>
+    <hyperlink ref="N29" r:id="rId47" xr:uid="{8C5E588B-27FD-4B7F-BE44-A579F0F4E123}"/>
+    <hyperlink ref="N44" r:id="rId48" xr:uid="{02C2221B-7A90-45B4-B72D-7C38424ED119}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId49"/>
